--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_sensor_availability_profile.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_sensor_availability_profile.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
   <si>
     <t>sensor_id</t>
   </si>
@@ -73,9 +73,24 @@
     <t>mean_Q_FA</t>
   </si>
   <si>
+    <t>mean_Q_TI_observed_weight</t>
+  </si>
+  <si>
     <t>mean_missing_rate</t>
   </si>
   <si>
+    <t>mean_true_irregular_rate</t>
+  </si>
+  <si>
+    <t>mean_duplicate_rate</t>
+  </si>
+  <si>
+    <t>mean_out_of_order_rate</t>
+  </si>
+  <si>
+    <t>mean_source_gap_recovery_rate</t>
+  </si>
+  <si>
     <t>mean_info_empty_cov</t>
   </si>
   <si>
@@ -181,7 +196,7 @@
     <t>process_floor</t>
   </si>
   <si>
-    <t>NorthBank_D2_v2_20260804</t>
+    <t>NorthBank_D2_v3_20260804</t>
   </si>
 </sst>
 </file>
@@ -539,10 +554,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:40">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -648,22 +663,37 @@
       <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:40">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -672,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4.957589100468003</v>
+        <v>4.957108394866681</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -696,78 +726,93 @@
         <v>0.008822087894134946</v>
       </c>
       <c r="Q2">
-        <v>4.973499889572631</v>
+        <v>4.966605874887303</v>
       </c>
       <c r="R2">
-        <v>4.957769006846772</v>
+        <v>4.959054935072007</v>
       </c>
       <c r="S2">
-        <v>4.979036952325631</v>
+        <v>4.979617830540882</v>
       </c>
       <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
         <v>0.003171458911942493</v>
       </c>
-      <c r="U2">
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z2">
         <v>0.003681315689157545</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
         <v>0.1480499736789559</v>
       </c>
-      <c r="Z2">
+      <c r="AE2">
         <v>0.07883924195392909</v>
       </c>
-      <c r="AA2">
+      <c r="AF2">
         <v>0.2089064967597887</v>
       </c>
-      <c r="AB2">
+      <c r="AG2">
         <v>565</v>
       </c>
-      <c r="AC2">
+      <c r="AH2">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD2">
+      <c r="AI2">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AE2">
-        <v>0.007841855905897728</v>
-      </c>
-      <c r="AF2">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG2">
+      <c r="AJ2">
+        <v>0.007678483907858193</v>
+      </c>
+      <c r="AK2">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL2">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH2">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>55</v>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:40">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -776,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>4.957567690549783</v>
+        <v>4.957092686420789</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -794,84 +839,99 @@
         <v>5</v>
       </c>
       <c r="O3">
-        <v>0.01045580787453031</v>
+        <v>0.01061917987256984</v>
       </c>
       <c r="P3">
         <v>0.008822087894134946</v>
       </c>
       <c r="Q3">
-        <v>4.973444184259411</v>
+        <v>4.966580064380669</v>
       </c>
       <c r="R3">
-        <v>4.957683407345799</v>
+        <v>4.959088297614273</v>
       </c>
       <c r="S3">
-        <v>4.979022581640618</v>
+        <v>4.979600434448498</v>
       </c>
       <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
         <v>0.003174181778576485</v>
       </c>
-      <c r="U3">
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z3">
         <v>0.003752110221641344</v>
       </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>6.807166584980667E-05</v>
       </c>
-      <c r="Y3">
+      <c r="AD3">
         <v>0.3188013941077166</v>
       </c>
-      <c r="Z3">
+      <c r="AE3">
         <v>0.1079793606709143</v>
       </c>
-      <c r="AA3">
+      <c r="AF3">
         <v>0.379582584545009</v>
       </c>
-      <c r="AB3">
+      <c r="AG3">
         <v>565</v>
       </c>
-      <c r="AC3">
+      <c r="AH3">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD3">
+      <c r="AI3">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AE3">
-        <v>0.007841855905897728</v>
-      </c>
-      <c r="AF3">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG3">
+      <c r="AJ3">
+        <v>0.007678483907858193</v>
+      </c>
+      <c r="AK3">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL3">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH3">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>55</v>
+      <c r="AM3">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:40">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -880,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>4.95750429806286</v>
+        <v>4.957029649360787</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -898,84 +958,99 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>0.01045580787453031</v>
+        <v>0.01061917987256984</v>
       </c>
       <c r="P4">
         <v>0.008822087894134946</v>
       </c>
       <c r="Q4">
-        <v>4.973436582923391</v>
+        <v>4.966574164836295</v>
       </c>
       <c r="R4">
-        <v>4.957594052764204</v>
+        <v>4.95889939502854</v>
       </c>
       <c r="S4">
-        <v>4.979053592066172</v>
+        <v>4.979646571910908</v>
       </c>
       <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
         <v>0.003160567445406524</v>
       </c>
-      <c r="U4">
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z4">
         <v>0.003692207155693514</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
         <v>2.178293307193814E-05</v>
       </c>
-      <c r="Y4">
+      <c r="AD4">
         <v>0.06251974078309644</v>
       </c>
-      <c r="Z4">
+      <c r="AE4">
         <v>0.06833896059104358</v>
       </c>
-      <c r="AA4">
+      <c r="AF4">
         <v>0.1203293761004919</v>
       </c>
-      <c r="AB4">
+      <c r="AG4">
         <v>565</v>
       </c>
-      <c r="AC4">
+      <c r="AH4">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD4">
+      <c r="AI4">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AE4">
-        <v>0.008005227903937265</v>
-      </c>
-      <c r="AF4">
-        <v>0.00245057997059304</v>
-      </c>
-      <c r="AG4">
+      <c r="AJ4">
+        <v>0.007678483907858193</v>
+      </c>
+      <c r="AK4">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL4">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH4">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>55</v>
+      <c r="AM4">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:40">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -984,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>4.957453871224636</v>
+        <v>4.956977065659453</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -1002,84 +1077,99 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>0.01045580787453031</v>
+        <v>0.01061917987256984</v>
       </c>
       <c r="P5">
         <v>0.008822087894134946</v>
       </c>
       <c r="Q5">
-        <v>4.97340368161823</v>
+        <v>4.96652623103826</v>
       </c>
       <c r="R5">
-        <v>4.957583948453659</v>
+        <v>4.958757912402905</v>
       </c>
       <c r="S5">
-        <v>4.979017287177719</v>
+        <v>4.979601190800341</v>
       </c>
       <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
         <v>0.003174181778576485</v>
       </c>
-      <c r="U5">
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z5">
         <v>0.003694930022327507</v>
       </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
         <v>1.089146653596907E-05</v>
       </c>
-      <c r="Y5">
+      <c r="AD5">
         <v>0.07205158924649203</v>
       </c>
-      <c r="Z5">
+      <c r="AE5">
         <v>0.05684664815117355</v>
       </c>
-      <c r="AA5">
+      <c r="AF5">
         <v>0.116784203743034</v>
       </c>
-      <c r="AB5">
+      <c r="AG5">
         <v>565</v>
       </c>
-      <c r="AC5">
+      <c r="AH5">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD5">
+      <c r="AI5">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AE5">
-        <v>0.007841855905897728</v>
-      </c>
-      <c r="AF5">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG5">
+      <c r="AJ5">
+        <v>0.007678483907858193</v>
+      </c>
+      <c r="AK5">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL5">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH5">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>55</v>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:40">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -1088,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>4.957218190898529</v>
+        <v>4.956736024689662</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -1106,84 +1196,99 @@
         <v>5</v>
       </c>
       <c r="O6">
-        <v>0.01045580787453031</v>
+        <v>0.01061917987256984</v>
       </c>
       <c r="P6">
         <v>0.008822087894134946</v>
       </c>
       <c r="Q6">
-        <v>4.973426750349435</v>
+        <v>4.966523772894771</v>
       </c>
       <c r="R6">
-        <v>4.957520164065091</v>
+        <v>4.958694128014337</v>
       </c>
       <c r="S6">
-        <v>4.9786580200524</v>
+        <v>4.979241923675023</v>
       </c>
       <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
         <v>0.003171458911942493</v>
       </c>
-      <c r="U6">
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z6">
         <v>0.003790230354517236</v>
       </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
         <v>0.0001089146653596907</v>
       </c>
-      <c r="Y6">
+      <c r="AD6">
         <v>0.07904481838479552</v>
       </c>
-      <c r="Z6">
+      <c r="AE6">
         <v>0.03145546297809</v>
       </c>
-      <c r="AA6">
+      <c r="AF6">
         <v>0.09343607616765598</v>
       </c>
-      <c r="AB6">
+      <c r="AG6">
         <v>565</v>
       </c>
-      <c r="AC6">
+      <c r="AH6">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD6">
+      <c r="AI6">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AE6">
-        <v>0.007841855905897728</v>
-      </c>
-      <c r="AF6">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG6">
+      <c r="AJ6">
+        <v>0.007678483907858193</v>
+      </c>
+      <c r="AK6">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL6">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH6">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>55</v>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:40">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -1192,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>4.956797371300546</v>
+        <v>4.956327680165072</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1216,78 +1321,93 @@
         <v>0.008822087894134946</v>
       </c>
       <c r="Q7">
-        <v>4.973449856898232</v>
+        <v>4.966611036988631</v>
       </c>
       <c r="R7">
-        <v>4.957586319822964</v>
+        <v>4.958991210091439</v>
       </c>
       <c r="S7">
-        <v>4.97776703758161</v>
+        <v>4.978344890389491</v>
       </c>
       <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
         <v>0.003166013178674508</v>
       </c>
-      <c r="U7">
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z7">
         <v>0.004313020748243752</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <v>0.0006371507923541904</v>
       </c>
-      <c r="Y7">
+      <c r="AD7">
         <v>0.2784185590589773</v>
       </c>
-      <c r="Z7">
+      <c r="AE7">
         <v>0.09703706729111077</v>
       </c>
-      <c r="AA7">
+      <c r="AF7">
         <v>0.3069455789722086</v>
       </c>
-      <c r="AB7">
+      <c r="AG7">
         <v>565</v>
       </c>
-      <c r="AC7">
+      <c r="AH7">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD7">
+      <c r="AI7">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AE7">
-        <v>0.007841855905897728</v>
-      </c>
-      <c r="AF7">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG7">
+      <c r="AJ7">
+        <v>0.007678483907858193</v>
+      </c>
+      <c r="AK7">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL7">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH7">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="s">
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:35">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -1296,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>4.956700539086338</v>
+        <v>4.95622493668785</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1314,84 +1434,99 @@
         <v>5</v>
       </c>
       <c r="O8">
-        <v>0.01045580787453031</v>
+        <v>0.01061917987256984</v>
       </c>
       <c r="P8">
         <v>0.008822087894134946</v>
       </c>
       <c r="Q8">
-        <v>4.97339819806737</v>
+        <v>4.966526476852608</v>
       </c>
       <c r="R8">
-        <v>4.957629855985108</v>
+        <v>4.958803819934354</v>
       </c>
       <c r="S8">
-        <v>4.977680057119691</v>
+        <v>4.978263960742314</v>
       </c>
       <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
         <v>0.003176904645210477</v>
       </c>
-      <c r="U8">
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z8">
         <v>0.003806567554321189</v>
       </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
         <v>0.0001198061318956597</v>
       </c>
-      <c r="Y8">
+      <c r="AD8">
         <v>0.003379077492784403</v>
       </c>
-      <c r="Z8">
+      <c r="AE8">
         <v>0.0006453193922561673</v>
       </c>
-      <c r="AA8">
+      <c r="AF8">
         <v>0.0007787398573217884</v>
       </c>
-      <c r="AB8">
+      <c r="AG8">
         <v>565</v>
       </c>
-      <c r="AC8">
+      <c r="AH8">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD8">
+      <c r="AI8">
         <v>0.979251756248979</v>
       </c>
-      <c r="AE8">
-        <v>0.008822087894134946</v>
-      </c>
-      <c r="AF8">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG8">
+      <c r="AJ8">
+        <v>0.008658715896095409</v>
+      </c>
+      <c r="AK8">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL8">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH8">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="s">
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:35">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -1400,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4.956649193206365</v>
+        <v>4.956173519332628</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1418,84 +1553,99 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>0.01045580787453031</v>
+        <v>0.01061917987256984</v>
       </c>
       <c r="P9">
         <v>0.008822087894134946</v>
       </c>
       <c r="Q9">
-        <v>4.973387230965649</v>
+        <v>4.966515169392559</v>
       </c>
       <c r="R9">
-        <v>4.957531684266286</v>
+        <v>4.958705648215532</v>
       </c>
       <c r="S9">
-        <v>4.977680057119691</v>
+        <v>4.978263960742314</v>
       </c>
       <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
         <v>0.003182350378478462</v>
       </c>
-      <c r="U9">
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z9">
         <v>0.003812013287589174</v>
       </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
         <v>0.0001198061318956597</v>
       </c>
-      <c r="Y9">
+      <c r="AD9">
         <v>0.004029842618308555</v>
       </c>
-      <c r="Z9">
+      <c r="AE9">
         <v>0.001584708380983499</v>
       </c>
-      <c r="AA9">
+      <c r="AF9">
         <v>0.002295376572455481</v>
       </c>
-      <c r="AB9">
+      <c r="AG9">
         <v>565</v>
       </c>
-      <c r="AC9">
+      <c r="AH9">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD9">
+      <c r="AI9">
         <v>0.979251756248979</v>
       </c>
-      <c r="AE9">
-        <v>0.008822087894134946</v>
-      </c>
-      <c r="AF9">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG9">
+      <c r="AJ9">
+        <v>0.008658715896095409</v>
+      </c>
+      <c r="AK9">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL9">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH9">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="s">
+      <c r="AM9">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:35">
-      <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1504,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>4.956541941713327</v>
+        <v>4.956067399531034</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1522,84 +1672,99 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>0.01045580787453031</v>
+        <v>0.01061917987256984</v>
       </c>
       <c r="P10">
         <v>0.008822087894134946</v>
       </c>
       <c r="Q10">
-        <v>4.973243940109036</v>
+        <v>4.966377267542825</v>
       </c>
       <c r="R10">
-        <v>4.957402159975841</v>
+        <v>4.958576123925086</v>
       </c>
       <c r="S10">
-        <v>4.977684595230747</v>
+        <v>4.978268498853371</v>
       </c>
       <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
         <v>0.003185073245112454</v>
       </c>
-      <c r="U10">
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z10">
         <v>0.003814736154223166</v>
       </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
         <v>0.0001198061318956597</v>
       </c>
-      <c r="Y10">
+      <c r="AD10">
         <v>0.003373631759516419</v>
       </c>
-      <c r="Z10">
+      <c r="AE10">
         <v>0.0008032456570277189</v>
       </c>
-      <c r="AA10">
+      <c r="AF10">
         <v>0.0009257746555573707</v>
       </c>
-      <c r="AB10">
+      <c r="AG10">
         <v>565</v>
       </c>
-      <c r="AC10">
+      <c r="AH10">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD10">
+      <c r="AI10">
         <v>0.979251756248979</v>
       </c>
-      <c r="AE10">
-        <v>0.008822087894134946</v>
-      </c>
-      <c r="AF10">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG10">
+      <c r="AJ10">
+        <v>0.008658715896095409</v>
+      </c>
+      <c r="AK10">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL10">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH10">
-        <v>1</v>
-      </c>
-      <c r="AI10" t="s">
+      <c r="AM10">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="1:35">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F11">
         <v>0.2</v>
@@ -1611,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>4.956399131404169</v>
+        <v>4.955913610018526</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1629,84 +1794,99 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>0.01045580787453031</v>
+        <v>0.01061917987256984</v>
       </c>
       <c r="P11">
         <v>0.008822087894134946</v>
       </c>
       <c r="Q11">
-        <v>4.973443390089976</v>
+        <v>4.966525493595213</v>
       </c>
       <c r="R11">
-        <v>4.956971709415672</v>
+        <v>4.958145673364919</v>
       </c>
       <c r="S11">
-        <v>4.977722412822887</v>
+        <v>4.978304803741824</v>
       </c>
       <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
         <v>0.003217747644720362</v>
       </c>
-      <c r="U11">
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z11">
         <v>0.003847410553831073</v>
       </c>
-      <c r="V11">
+      <c r="AA11">
         <v>0.9609395705131697</v>
       </c>
-      <c r="W11">
+      <c r="AB11">
         <v>0.5780541487411279</v>
       </c>
-      <c r="X11">
+      <c r="AC11">
         <v>0.0001198061318956597</v>
       </c>
-      <c r="Y11">
+      <c r="AD11">
         <v>0.5817027900306776</v>
       </c>
-      <c r="Z11">
+      <c r="AE11">
         <v>0.03074343335330102</v>
       </c>
-      <c r="AA11">
+      <c r="AF11">
         <v>0.5849479932472906</v>
       </c>
-      <c r="AB11">
+      <c r="AG11">
         <v>565</v>
       </c>
-      <c r="AC11">
+      <c r="AH11">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AD11">
+      <c r="AI11">
         <v>0.979251756248979</v>
       </c>
-      <c r="AE11">
-        <v>0.008822087894134946</v>
-      </c>
-      <c r="AF11">
-        <v>0.002613951968632576</v>
-      </c>
-      <c r="AG11">
+      <c r="AJ11">
+        <v>0.008658715896095409</v>
+      </c>
+      <c r="AK11">
+        <v>0.002777323966672113</v>
+      </c>
+      <c r="AL11">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>55</v>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:40">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -1715,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>4.948874142343767</v>
+        <v>4.948402068699988</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1739,78 +1919,93 @@
         <v>0.008822087894134946</v>
       </c>
       <c r="Q12">
-        <v>4.97347103474983</v>
+        <v>4.966620869562586</v>
       </c>
       <c r="R12">
-        <v>4.957581309748358</v>
+        <v>4.958986200016833</v>
       </c>
       <c r="S12">
-        <v>4.96507394095615</v>
+        <v>4.966936079193064</v>
       </c>
       <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
         <v>0.003160567445406524</v>
       </c>
-      <c r="U12">
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z12">
         <v>0.006194521592332407</v>
       </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
         <v>0.002524097369710831</v>
       </c>
-      <c r="Y12">
+      <c r="AD12">
         <v>0.005862331862985351</v>
       </c>
-      <c r="Z12">
+      <c r="AE12">
         <v>0.002957033164515602</v>
       </c>
-      <c r="AA12">
+      <c r="AF12">
         <v>0.003076839296411261</v>
       </c>
-      <c r="AB12">
+      <c r="AG12">
         <v>565</v>
       </c>
-      <c r="AC12">
+      <c r="AH12">
         <v>0.01241627185100474</v>
       </c>
-      <c r="AD12">
+      <c r="AI12">
         <v>0.9764744322823068</v>
       </c>
-      <c r="AE12">
-        <v>0.008331971900016338</v>
-      </c>
-      <c r="AF12">
-        <v>0.005881391929423297</v>
-      </c>
-      <c r="AG12">
+      <c r="AJ12">
+        <v>0.008168599901976801</v>
+      </c>
+      <c r="AK12">
+        <v>0.006044763927462833</v>
+      </c>
+      <c r="AL12">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH12">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>55</v>
+      <c r="AM12">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:40">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -1819,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>4.948820416221793</v>
+        <v>4.948353179069874</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1843,78 +2038,93 @@
         <v>0.008822087894134946</v>
       </c>
       <c r="Q13">
-        <v>4.973439646148354</v>
+        <v>4.966612511874724</v>
       </c>
       <c r="R13">
-        <v>4.957500059407999</v>
+        <v>4.958904949676474</v>
       </c>
       <c r="S13">
-        <v>4.965056544863766</v>
+        <v>4.96691868310068</v>
       </c>
       <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
         <v>0.003193241845014431</v>
       </c>
-      <c r="U13">
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z13">
         <v>0.006227195991940313</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
         <v>0.002524097369710831</v>
       </c>
-      <c r="Y13">
+      <c r="AD13">
         <v>0.006679191853183032</v>
       </c>
-      <c r="Z13">
+      <c r="AE13">
         <v>0.005772477264063605</v>
       </c>
-      <c r="AA13">
+      <c r="AF13">
         <v>0.006793552251810706</v>
       </c>
-      <c r="AB13">
+      <c r="AG13">
         <v>565</v>
       </c>
-      <c r="AC13">
+      <c r="AH13">
         <v>0.01241627185100474</v>
       </c>
-      <c r="AD13">
+      <c r="AI13">
         <v>0.9764744322823068</v>
       </c>
-      <c r="AE13">
-        <v>0.008331971900016338</v>
-      </c>
-      <c r="AF13">
-        <v>0.005881391929423297</v>
-      </c>
-      <c r="AG13">
+      <c r="AJ13">
+        <v>0.008168599901976801</v>
+      </c>
+      <c r="AK13">
+        <v>0.006044763927462833</v>
+      </c>
+      <c r="AL13">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH13">
-        <v>1</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>55</v>
+      <c r="AM13">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:40">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F14">
         <v>0.2</v>
@@ -1926,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>4.948800349838856</v>
+        <v>4.948324468816852</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1950,78 +2160,93 @@
         <v>0.008822087894134946</v>
       </c>
       <c r="Q14">
-        <v>4.973503709149437</v>
+        <v>4.966632668651334</v>
       </c>
       <c r="R14">
-        <v>4.957494017119404</v>
+        <v>4.958779945344641</v>
       </c>
       <c r="S14">
-        <v>4.965077722715364</v>
+        <v>4.966942886359648</v>
       </c>
       <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
         <v>0.003193241845014431</v>
       </c>
-      <c r="U14">
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z14">
         <v>0.006246256058378261</v>
       </c>
-      <c r="V14">
+      <c r="AA14">
         <v>0.6988654722358365</v>
       </c>
-      <c r="W14">
+      <c r="AB14">
         <v>0.1688395142405925</v>
       </c>
-      <c r="X14">
+      <c r="AC14">
         <v>0.002543157436148778</v>
       </c>
-      <c r="Y14">
+      <c r="AD14">
         <v>0.1738904318466482</v>
       </c>
-      <c r="Z14">
+      <c r="AE14">
         <v>0.04360217103232951</v>
       </c>
-      <c r="AA14">
+      <c r="AF14">
         <v>0.1935967252990615</v>
       </c>
-      <c r="AB14">
+      <c r="AG14">
         <v>565</v>
       </c>
-      <c r="AC14">
+      <c r="AH14">
         <v>0.01241627185100474</v>
       </c>
-      <c r="AD14">
+      <c r="AI14">
         <v>0.9764744322823068</v>
       </c>
-      <c r="AE14">
-        <v>0.008331971900016338</v>
-      </c>
-      <c r="AF14">
-        <v>0.005881391929423297</v>
-      </c>
-      <c r="AG14">
+      <c r="AJ14">
+        <v>0.008168599901976801</v>
+      </c>
+      <c r="AK14">
+        <v>0.006044763927462833</v>
+      </c>
+      <c r="AL14">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>55</v>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:40">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -2030,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>4.93851410653807</v>
+        <v>4.938046881298692</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -2054,61 +2279,76 @@
         <v>0.008822087894134946</v>
       </c>
       <c r="Q15">
-        <v>4.973434918949336</v>
+        <v>4.966607841402095</v>
       </c>
       <c r="R15">
-        <v>4.957570962855148</v>
+        <v>4.958975853123623</v>
       </c>
       <c r="S15">
-        <v>4.947436572334465</v>
+        <v>4.949298710571378</v>
       </c>
       <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
         <v>0.003187796111746446</v>
       </c>
-      <c r="U15">
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>8.897964722386656E-05</v>
+      </c>
+      <c r="Z15">
         <v>0.008133202635734901</v>
       </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
         <v>0.004435549746773403</v>
       </c>
-      <c r="Y15">
+      <c r="AD15">
         <v>0.02123563687850569</v>
       </c>
-      <c r="Z15">
+      <c r="AE15">
         <v>0.0183189929023943</v>
       </c>
-      <c r="AA15">
+      <c r="AF15">
         <v>0.02782724318829531</v>
       </c>
-      <c r="AB15">
+      <c r="AG15">
         <v>565</v>
       </c>
-      <c r="AC15">
+      <c r="AH15">
         <v>0.01257964384904427</v>
       </c>
-      <c r="AD15">
+      <c r="AI15">
         <v>0.966181996405816</v>
       </c>
-      <c r="AE15">
-        <v>0.01797091978434896</v>
-      </c>
-      <c r="AF15">
-        <v>0.006534879921581441</v>
-      </c>
-      <c r="AG15">
+      <c r="AJ15">
+        <v>0.01780754778630943</v>
+      </c>
+      <c r="AK15">
+        <v>0.006698251919620977</v>
+      </c>
+      <c r="AL15">
         <v>0.009312203888253554</v>
       </c>
-      <c r="AH15">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>55</v>
+      <c r="AM15">
+        <v>1</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_sensor_availability_profile.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_sensor_availability_profile.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="65">
   <si>
     <t>sensor_id</t>
   </si>
@@ -70,6 +70,9 @@
     <t>mean_Q_GS</t>
   </si>
   <si>
+    <t>mean_Q_HA</t>
+  </si>
+  <si>
     <t>mean_Q_FA</t>
   </si>
   <si>
@@ -94,6 +97,12 @@
     <t>mean_info_empty_cov</t>
   </si>
   <si>
+    <t>mean_hard_stasis_fraction_observed</t>
+  </si>
+  <si>
+    <t>mean_qha_observed_fraction</t>
+  </si>
+  <si>
     <t>mean_floor_occupancy</t>
   </si>
   <si>
@@ -112,6 +121,9 @@
     <t>mean_soft_stasis_cov</t>
   </si>
   <si>
+    <t>sensitive_suspect_rate</t>
+  </si>
+  <si>
     <t>max_L_max_min</t>
   </si>
   <si>
@@ -196,7 +208,7 @@
     <t>process_floor</t>
   </si>
   <si>
-    <t>NorthBank_D2_v3_20260804</t>
+    <t>NorthBank_D2_v4_20260805</t>
   </si>
 </sst>
 </file>
@@ -554,10 +566,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AR15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:44">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,22 +690,34 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:44">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -702,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4.957108394866681</v>
+        <v>4.95969311097208</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -720,7 +744,7 @@
         <v>5</v>
       </c>
       <c r="O2">
-        <v>0.01045580787453031</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P2">
         <v>0.008822087894134946</v>
@@ -732,17 +756,17 @@
         <v>4.959054935072007</v>
       </c>
       <c r="S2">
-        <v>4.979617830540882</v>
+        <v>5</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
         <v>0.003171458911942493</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
       <c r="W2">
         <v>0</v>
       </c>
@@ -750,69 +774,81 @@
         <v>0</v>
       </c>
       <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>0.003681315689157545</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
       <c r="AB2">
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>0.9963186843108426</v>
       </c>
       <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
         <v>0.1480499736789559</v>
       </c>
-      <c r="AE2">
+      <c r="AH2">
         <v>0.07883924195392909</v>
       </c>
-      <c r="AF2">
+      <c r="AI2">
         <v>0.2089064967597887</v>
       </c>
-      <c r="AG2">
+      <c r="AJ2">
+        <v>0.00163371998039536</v>
+      </c>
+      <c r="AK2">
         <v>565</v>
       </c>
-      <c r="AH2">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI2">
+      <c r="AL2">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AM2">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AJ2">
-        <v>0.007678483907858193</v>
-      </c>
-      <c r="AK2">
-        <v>0.002777323966672113</v>
-      </c>
-      <c r="AL2">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AM2">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>60</v>
+      <c r="AN2">
+        <v>0.009965691880411697</v>
+      </c>
+      <c r="AO2">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP2">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:44">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -821,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>4.957092686420789</v>
+        <v>4.959678129827932</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -839,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="O3">
-        <v>0.01061917987256984</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P3">
         <v>0.008822087894134946</v>
@@ -851,17 +887,17 @@
         <v>4.959088297614273</v>
       </c>
       <c r="S3">
-        <v>4.979600434448498</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
         <v>0.003174181778576485</v>
       </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
       <c r="W3">
         <v>0</v>
       </c>
@@ -869,69 +905,81 @@
         <v>0</v>
       </c>
       <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>0.003752110221641344</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
       <c r="AB3">
-        <v>0</v>
+        <v>6.809391512774417E-05</v>
       </c>
       <c r="AC3">
+        <v>0.9963159614442085</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
         <v>6.807166584980667E-05</v>
       </c>
-      <c r="AD3">
+      <c r="AG3">
         <v>0.3188013941077166</v>
       </c>
-      <c r="AE3">
+      <c r="AH3">
         <v>0.1079793606709143</v>
       </c>
-      <c r="AF3">
+      <c r="AI3">
         <v>0.379582584545009</v>
       </c>
-      <c r="AG3">
+      <c r="AJ3">
+        <v>0.04247671949027937</v>
+      </c>
+      <c r="AK3">
         <v>565</v>
       </c>
-      <c r="AH3">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI3">
+      <c r="AL3">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AM3">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AJ3">
-        <v>0.007678483907858193</v>
-      </c>
-      <c r="AK3">
-        <v>0.002777323966672113</v>
-      </c>
-      <c r="AL3">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AM3">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="AN3">
+        <v>0.009965691880411697</v>
+      </c>
+      <c r="AO3">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP3">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:40">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -940,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>4.957029649360787</v>
+        <v>4.959584550737319</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -958,7 +1006,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>0.01061917987256984</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P4">
         <v>0.008822087894134946</v>
@@ -970,17 +1018,17 @@
         <v>4.95889939502854</v>
       </c>
       <c r="S4">
-        <v>4.979646571910908</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
         <v>0.003160567445406524</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
       <c r="W4">
         <v>0</v>
       </c>
@@ -988,69 +1036,81 @@
         <v>0</v>
       </c>
       <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>0.003692207155693514</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.179005284087814E-05</v>
       </c>
       <c r="AC4">
+        <v>0.9963295757773785</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>2.178293307193814E-05</v>
       </c>
-      <c r="AD4">
+      <c r="AG4">
         <v>0.06251974078309644</v>
       </c>
-      <c r="AE4">
+      <c r="AH4">
         <v>0.06833896059104358</v>
       </c>
-      <c r="AF4">
+      <c r="AI4">
         <v>0.1203293761004919</v>
       </c>
-      <c r="AG4">
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
         <v>565</v>
       </c>
-      <c r="AH4">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI4">
-        <v>0.9802319882372161</v>
-      </c>
-      <c r="AJ4">
-        <v>0.007678483907858193</v>
-      </c>
-      <c r="AK4">
-        <v>0.002777323966672113</v>
-      </c>
       <c r="AL4">
         <v>0.009312203888253554</v>
       </c>
       <c r="AM4">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="s">
+        <v>0.9803953602352556</v>
+      </c>
+      <c r="AN4">
+        <v>0.009802319882372162</v>
+      </c>
+      <c r="AO4">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP4">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:40">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" t="s">
-        <v>56</v>
-      </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -1059,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>4.956977065659453</v>
+        <v>4.959549489076767</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -1077,7 +1137,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>0.01061917987256984</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P5">
         <v>0.008822087894134946</v>
@@ -1089,17 +1149,17 @@
         <v>4.958757912402905</v>
       </c>
       <c r="S5">
-        <v>4.979601190800341</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
         <v>0.003174181778576485</v>
       </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
       <c r="W5">
         <v>0</v>
       </c>
@@ -1107,69 +1167,81 @@
         <v>0</v>
       </c>
       <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0.003694930022327507</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.089502642043907E-05</v>
       </c>
       <c r="AC5">
+        <v>0.9963159614442085</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>1.089146653596907E-05</v>
       </c>
-      <c r="AD5">
+      <c r="AG5">
         <v>0.07205158924649203</v>
       </c>
-      <c r="AE5">
+      <c r="AH5">
         <v>0.05684664815117355</v>
       </c>
-      <c r="AF5">
+      <c r="AI5">
         <v>0.116784203743034</v>
       </c>
-      <c r="AG5">
+      <c r="AJ5">
+        <v>0.000326743996079072</v>
+      </c>
+      <c r="AK5">
         <v>565</v>
       </c>
-      <c r="AH5">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI5">
-        <v>0.9802319882372161</v>
-      </c>
-      <c r="AJ5">
-        <v>0.007678483907858193</v>
-      </c>
-      <c r="AK5">
-        <v>0.002777323966672113</v>
-      </c>
       <c r="AL5">
         <v>0.009312203888253554</v>
       </c>
       <c r="AM5">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="s">
+        <v>0.9803953602352556</v>
+      </c>
+      <c r="AN5">
+        <v>0.009802319882372162</v>
+      </c>
+      <c r="AO5">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP5">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:40">
-      <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" t="s">
-        <v>56</v>
-      </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -1178,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>4.956736024689662</v>
+        <v>4.959297978162197</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -1196,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="O6">
-        <v>0.01061917987256984</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P6">
         <v>0.008822087894134946</v>
@@ -1208,17 +1280,17 @@
         <v>4.958694128014337</v>
       </c>
       <c r="S6">
-        <v>4.979241923675023</v>
+        <v>4.999623213669627</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>4.999623213669627</v>
       </c>
       <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
         <v>0.003171458911942493</v>
       </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
       <c r="W6">
         <v>0</v>
       </c>
@@ -1226,69 +1298,81 @@
         <v>0</v>
       </c>
       <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0.003790230354517236</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
       <c r="AB6">
-        <v>0</v>
+        <v>0.0001089502642043907</v>
       </c>
       <c r="AC6">
+        <v>0.9963186843108426</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
         <v>0.0001089146653596907</v>
       </c>
-      <c r="AD6">
+      <c r="AG6">
         <v>0.07904481838479552</v>
       </c>
-      <c r="AE6">
+      <c r="AH6">
         <v>0.03145546297809</v>
       </c>
-      <c r="AF6">
+      <c r="AI6">
         <v>0.09343607616765598</v>
       </c>
-      <c r="AG6">
+      <c r="AJ6">
+        <v>0.005391275935304689</v>
+      </c>
+      <c r="AK6">
         <v>565</v>
       </c>
-      <c r="AH6">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI6">
-        <v>0.9802319882372161</v>
-      </c>
-      <c r="AJ6">
-        <v>0.007678483907858193</v>
-      </c>
-      <c r="AK6">
-        <v>0.002777323966672113</v>
-      </c>
       <c r="AL6">
         <v>0.009312203888253554</v>
       </c>
       <c r="AM6">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>60</v>
+        <v>0.9803953602352556</v>
+      </c>
+      <c r="AN6">
+        <v>0.009802319882372162</v>
+      </c>
+      <c r="AO6">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP6">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:44">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -1297,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>4.956327680165072</v>
+        <v>4.958891111258255</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1315,7 +1399,7 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>0.01045580787453031</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P7">
         <v>0.008822087894134946</v>
@@ -1327,17 +1411,17 @@
         <v>4.958991210091439</v>
       </c>
       <c r="S7">
-        <v>4.978344890389491</v>
+        <v>4.99871680799937</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>4.99871680799937</v>
       </c>
       <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
         <v>0.003166013178674508</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
       <c r="W7">
         <v>0</v>
       </c>
@@ -1345,69 +1429,81 @@
         <v>0</v>
       </c>
       <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>0.004313020748243752</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
       <c r="AB7">
-        <v>0</v>
+        <v>0.0006373590455956855</v>
       </c>
       <c r="AC7">
+        <v>0.9963241300441105</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>0.0006371507923541904</v>
       </c>
-      <c r="AD7">
+      <c r="AG7">
         <v>0.2784185590589773</v>
       </c>
-      <c r="AE7">
+      <c r="AH7">
         <v>0.09703706729111077</v>
       </c>
-      <c r="AF7">
+      <c r="AI7">
         <v>0.3069455789722086</v>
       </c>
-      <c r="AG7">
+      <c r="AJ7">
+        <v>0.1003104067962751</v>
+      </c>
+      <c r="AK7">
         <v>565</v>
       </c>
-      <c r="AH7">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI7">
+      <c r="AL7">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AM7">
         <v>0.9802319882372161</v>
       </c>
-      <c r="AJ7">
-        <v>0.007678483907858193</v>
-      </c>
-      <c r="AK7">
-        <v>0.002777323966672113</v>
-      </c>
-      <c r="AL7">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AM7">
-        <v>1</v>
-      </c>
-      <c r="AN7" t="s">
+      <c r="AN7">
+        <v>0.009965691880411697</v>
+      </c>
+      <c r="AO7">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP7">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:40">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
-      </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -1416,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>4.95622493668785</v>
+        <v>4.958802624313989</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1434,7 +1530,7 @@
         <v>5</v>
       </c>
       <c r="O8">
-        <v>0.01061917987256984</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P8">
         <v>0.008822087894134946</v>
@@ -1446,17 +1542,17 @@
         <v>4.958803819934354</v>
       </c>
       <c r="S8">
-        <v>4.978263960742314</v>
+        <v>4.998671412055952</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>4.998671412055952</v>
       </c>
       <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
         <v>0.003176904645210477</v>
       </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
       <c r="W8">
         <v>0</v>
       </c>
@@ -1464,69 +1560,81 @@
         <v>0</v>
       </c>
       <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>0.003806567554321189</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
       <c r="AB8">
-        <v>0</v>
+        <v>0.0001198452906248298</v>
       </c>
       <c r="AC8">
+        <v>0.9963132385775745</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>0.0001198061318956597</v>
       </c>
-      <c r="AD8">
+      <c r="AG8">
         <v>0.003379077492784403</v>
       </c>
-      <c r="AE8">
+      <c r="AH8">
         <v>0.0006453193922561673</v>
       </c>
-      <c r="AF8">
+      <c r="AI8">
         <v>0.0007787398573217884</v>
       </c>
-      <c r="AG8">
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
         <v>565</v>
       </c>
-      <c r="AH8">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI8">
-        <v>0.979251756248979</v>
-      </c>
-      <c r="AJ8">
-        <v>0.008658715896095409</v>
-      </c>
-      <c r="AK8">
-        <v>0.002777323966672113</v>
-      </c>
       <c r="AL8">
         <v>0.009312203888253554</v>
       </c>
       <c r="AM8">
-        <v>1</v>
-      </c>
-      <c r="AN8" t="s">
+        <v>0.9794151282470185</v>
+      </c>
+      <c r="AN8">
+        <v>0.01078255187060938</v>
+      </c>
+      <c r="AO8">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP8">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:44">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:40">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -1535,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4.956173519332628</v>
+        <v>4.958750182170779</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1553,7 +1661,7 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>0.01061917987256984</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P9">
         <v>0.008822087894134946</v>
@@ -1565,17 +1673,17 @@
         <v>4.958705648215532</v>
       </c>
       <c r="S9">
-        <v>4.978263960742314</v>
+        <v>4.998671412055952</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>4.998671412055952</v>
       </c>
       <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
         <v>0.003182350378478462</v>
       </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
       <c r="W9">
         <v>0</v>
       </c>
@@ -1583,69 +1691,81 @@
         <v>0</v>
       </c>
       <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>0.003812013287589174</v>
       </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
       <c r="AB9">
-        <v>0</v>
+        <v>0.0001198452906248298</v>
       </c>
       <c r="AC9">
+        <v>0.9963077928443066</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
         <v>0.0001198061318956597</v>
       </c>
-      <c r="AD9">
+      <c r="AG9">
         <v>0.004029842618308555</v>
       </c>
-      <c r="AE9">
+      <c r="AH9">
         <v>0.001584708380983499</v>
       </c>
-      <c r="AF9">
+      <c r="AI9">
         <v>0.002295376572455481</v>
       </c>
-      <c r="AG9">
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
         <v>565</v>
       </c>
-      <c r="AH9">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI9">
-        <v>0.979251756248979</v>
-      </c>
-      <c r="AJ9">
-        <v>0.008658715896095409</v>
-      </c>
-      <c r="AK9">
-        <v>0.002777323966672113</v>
-      </c>
       <c r="AL9">
         <v>0.009312203888253554</v>
       </c>
       <c r="AM9">
-        <v>1</v>
-      </c>
-      <c r="AN9" t="s">
+        <v>0.9794151282470185</v>
+      </c>
+      <c r="AN9">
+        <v>0.01078255187060938</v>
+      </c>
+      <c r="AO9">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP9">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:40">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>56</v>
-      </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1654,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>4.956067399531034</v>
+        <v>4.958655165394208</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1672,7 +1792,7 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>0.01061917987256984</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P10">
         <v>0.008822087894134946</v>
@@ -1684,17 +1804,17 @@
         <v>4.958576123925086</v>
       </c>
       <c r="S10">
-        <v>4.978268498853371</v>
+        <v>4.998671412055952</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>4.998671412055952</v>
       </c>
       <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
         <v>0.003185073245112454</v>
       </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
       <c r="W10">
         <v>0</v>
       </c>
@@ -1702,69 +1822,81 @@
         <v>0</v>
       </c>
       <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>0.003814736154223166</v>
       </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
       <c r="AB10">
-        <v>0</v>
+        <v>0.0001198452906248298</v>
       </c>
       <c r="AC10">
+        <v>0.9963050699776727</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
         <v>0.0001198061318956597</v>
       </c>
-      <c r="AD10">
+      <c r="AG10">
         <v>0.003373631759516419</v>
       </c>
-      <c r="AE10">
+      <c r="AH10">
         <v>0.0008032456570277189</v>
       </c>
-      <c r="AF10">
+      <c r="AI10">
         <v>0.0009257746555573707</v>
       </c>
-      <c r="AG10">
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
         <v>565</v>
       </c>
-      <c r="AH10">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI10">
-        <v>0.979251756248979</v>
-      </c>
-      <c r="AJ10">
-        <v>0.008658715896095409</v>
-      </c>
-      <c r="AK10">
-        <v>0.002777323966672113</v>
-      </c>
       <c r="AL10">
         <v>0.009312203888253554</v>
       </c>
       <c r="AM10">
-        <v>1</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>60</v>
+        <v>0.9794151282470185</v>
+      </c>
+      <c r="AN10">
+        <v>0.01078255187060938</v>
+      </c>
+      <c r="AO10">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP10">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:44">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F11">
         <v>0.2</v>
@@ -1776,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>4.955913610018526</v>
+        <v>4.958468053604856</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1794,7 +1926,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>0.01061917987256984</v>
+        <v>0.009312203888253554</v>
       </c>
       <c r="P11">
         <v>0.008822087894134946</v>
@@ -1806,17 +1938,17 @@
         <v>4.958145673364919</v>
       </c>
       <c r="S11">
-        <v>4.978304803741824</v>
+        <v>4.998671412055952</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>4.998671412055952</v>
       </c>
       <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
         <v>0.003217747644720362</v>
       </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
       <c r="W11">
         <v>0</v>
       </c>
@@ -1824,69 +1956,81 @@
         <v>0</v>
       </c>
       <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>0.003847410553831073</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
+        <v>0.0001198452906248298</v>
+      </c>
+      <c r="AC11">
+        <v>0.9962723955780646</v>
+      </c>
+      <c r="AD11">
         <v>0.9609395705131697</v>
       </c>
-      <c r="AB11">
+      <c r="AE11">
         <v>0.5780541487411279</v>
       </c>
-      <c r="AC11">
+      <c r="AF11">
         <v>0.0001198061318956597</v>
       </c>
-      <c r="AD11">
+      <c r="AG11">
         <v>0.5817027900306776</v>
       </c>
-      <c r="AE11">
+      <c r="AH11">
         <v>0.03074343335330102</v>
       </c>
-      <c r="AF11">
+      <c r="AI11">
         <v>0.5849479932472906</v>
       </c>
-      <c r="AG11">
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
         <v>565</v>
       </c>
-      <c r="AH11">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AI11">
-        <v>0.979251756248979</v>
-      </c>
-      <c r="AJ11">
-        <v>0.008658715896095409</v>
-      </c>
-      <c r="AK11">
-        <v>0.002777323966672113</v>
-      </c>
       <c r="AL11">
         <v>0.009312203888253554</v>
       </c>
       <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>60</v>
+        <v>0.9794151282470185</v>
+      </c>
+      <c r="AN11">
+        <v>0.01078255187060938</v>
+      </c>
+      <c r="AO11">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="AP11">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:44">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -1895,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>4.948402068699988</v>
+        <v>4.950962435055505</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1913,7 +2057,7 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>0.01355987583728149</v>
+        <v>0.01241627185100474</v>
       </c>
       <c r="P12">
         <v>0.008822087894134946</v>
@@ -1925,17 +2069,17 @@
         <v>4.958986200016833</v>
       </c>
       <c r="S12">
-        <v>4.966936079193064</v>
+        <v>4.987291405639992</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>4.987291405639992</v>
       </c>
       <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
         <v>0.003160567445406524</v>
       </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
       <c r="W12">
         <v>0</v>
       </c>
@@ -1943,69 +2087,81 @@
         <v>0</v>
       </c>
       <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>0.006194521592332407</v>
       </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
       <c r="AB12">
-        <v>0</v>
+        <v>0.002524922372936754</v>
       </c>
       <c r="AC12">
+        <v>0.9963295757773785</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
         <v>0.002524097369710831</v>
       </c>
-      <c r="AD12">
+      <c r="AG12">
         <v>0.005862331862985351</v>
       </c>
-      <c r="AE12">
+      <c r="AH12">
         <v>0.002957033164515602</v>
       </c>
-      <c r="AF12">
+      <c r="AI12">
         <v>0.003076839296411261</v>
       </c>
-      <c r="AG12">
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
         <v>565</v>
       </c>
-      <c r="AH12">
+      <c r="AL12">
         <v>0.01241627185100474</v>
       </c>
-      <c r="AI12">
+      <c r="AM12">
         <v>0.9764744322823068</v>
       </c>
-      <c r="AJ12">
-        <v>0.008168599901976801</v>
-      </c>
-      <c r="AK12">
-        <v>0.006044763927462833</v>
-      </c>
-      <c r="AL12">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AM12">
-        <v>1</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>60</v>
+      <c r="AN12">
+        <v>0.01045580787453031</v>
+      </c>
+      <c r="AO12">
+        <v>0.003757555954909328</v>
+      </c>
+      <c r="AP12">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:44">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -2014,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>4.948353179069874</v>
+        <v>4.950919242267472</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -2032,7 +2188,7 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>0.01355987583728149</v>
+        <v>0.01241627185100474</v>
       </c>
       <c r="P13">
         <v>0.008822087894134946</v>
@@ -2044,17 +2200,17 @@
         <v>4.958904949676474</v>
       </c>
       <c r="S13">
-        <v>4.96691868310068</v>
+        <v>4.987291405639992</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>4.987291405639992</v>
       </c>
       <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
         <v>0.003193241845014431</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
       <c r="W13">
         <v>0</v>
       </c>
@@ -2062,69 +2218,81 @@
         <v>0</v>
       </c>
       <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>0.006227195991940313</v>
       </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
       <c r="AB13">
-        <v>0</v>
+        <v>0.002524922372936754</v>
       </c>
       <c r="AC13">
+        <v>0.9962969013777706</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
         <v>0.002524097369710831</v>
       </c>
-      <c r="AD13">
+      <c r="AG13">
         <v>0.006679191853183032</v>
       </c>
-      <c r="AE13">
+      <c r="AH13">
         <v>0.005772477264063605</v>
       </c>
-      <c r="AF13">
+      <c r="AI13">
         <v>0.006793552251810706</v>
       </c>
-      <c r="AG13">
+      <c r="AJ13">
+        <v>0.001470347982355824</v>
+      </c>
+      <c r="AK13">
         <v>565</v>
       </c>
-      <c r="AH13">
+      <c r="AL13">
         <v>0.01241627185100474</v>
       </c>
-      <c r="AI13">
+      <c r="AM13">
         <v>0.9764744322823068</v>
       </c>
-      <c r="AJ13">
-        <v>0.008168599901976801</v>
-      </c>
-      <c r="AK13">
-        <v>0.006044763927462833</v>
-      </c>
-      <c r="AL13">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AM13">
-        <v>1</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>60</v>
+      <c r="AN13">
+        <v>0.01045580787453031</v>
+      </c>
+      <c r="AO13">
+        <v>0.003757555954909328</v>
+      </c>
+      <c r="AP13">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ13">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:44">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F14">
         <v>0.2</v>
@@ -2136,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>4.948324468816852</v>
+        <v>4.950880157238672</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -2154,7 +2322,7 @@
         <v>5</v>
       </c>
       <c r="O14">
-        <v>0.01355987583728149</v>
+        <v>0.01241627185100474</v>
       </c>
       <c r="P14">
         <v>0.008822087894134946</v>
@@ -2166,17 +2334,17 @@
         <v>4.958779945344641</v>
       </c>
       <c r="S14">
-        <v>4.966942886359648</v>
+        <v>4.987280813253194</v>
       </c>
       <c r="T14">
-        <v>1</v>
+        <v>4.987280813253194</v>
       </c>
       <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
         <v>0.003193241845014431</v>
       </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
       <c r="W14">
         <v>0</v>
       </c>
@@ -2184,69 +2352,81 @@
         <v>0</v>
       </c>
       <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <v>0.006246256058378261</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
+        <v>0.002543988669172523</v>
+      </c>
+      <c r="AC14">
+        <v>0.9962969013777706</v>
+      </c>
+      <c r="AD14">
         <v>0.6988654722358365</v>
       </c>
-      <c r="AB14">
+      <c r="AE14">
         <v>0.1688395142405925</v>
       </c>
-      <c r="AC14">
+      <c r="AF14">
         <v>0.002543157436148778</v>
       </c>
-      <c r="AD14">
+      <c r="AG14">
         <v>0.1738904318466482</v>
       </c>
-      <c r="AE14">
+      <c r="AH14">
         <v>0.04360217103232951</v>
       </c>
-      <c r="AF14">
+      <c r="AI14">
         <v>0.1935967252990615</v>
       </c>
-      <c r="AG14">
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
         <v>565</v>
       </c>
-      <c r="AH14">
+      <c r="AL14">
         <v>0.01241627185100474</v>
       </c>
-      <c r="AI14">
+      <c r="AM14">
         <v>0.9764744322823068</v>
       </c>
-      <c r="AJ14">
-        <v>0.008168599901976801</v>
-      </c>
-      <c r="AK14">
-        <v>0.006044763927462833</v>
-      </c>
-      <c r="AL14">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>60</v>
+      <c r="AN14">
+        <v>0.01045580787453031</v>
+      </c>
+      <c r="AO14">
+        <v>0.003757555954909328</v>
+      </c>
+      <c r="AP14">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:44">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -2255,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>4.938046881298692</v>
+        <v>4.940616378333655</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -2273,7 +2453,7 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>0.01372324783532103</v>
+        <v>0.01257964384904427</v>
       </c>
       <c r="P15">
         <v>0.008822087894134946</v>
@@ -2285,17 +2465,17 @@
         <v>4.958975853123623</v>
       </c>
       <c r="S15">
-        <v>4.949298710571378</v>
+        <v>4.969675509796445</v>
       </c>
       <c r="T15">
-        <v>1</v>
+        <v>4.969675509796445</v>
       </c>
       <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
         <v>0.003187796111746446</v>
       </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
       <c r="W15">
         <v>0</v>
       </c>
@@ -2303,52 +2483,64 @@
         <v>0</v>
       </c>
       <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
         <v>8.897964722386656E-05</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <v>0.008133202635734901</v>
       </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
       <c r="AB15">
-        <v>0</v>
+        <v>0.004436999509723811</v>
       </c>
       <c r="AC15">
+        <v>0.9963023471110385</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
         <v>0.004435549746773403</v>
       </c>
-      <c r="AD15">
+      <c r="AG15">
         <v>0.02123563687850569</v>
       </c>
-      <c r="AE15">
+      <c r="AH15">
         <v>0.0183189929023943</v>
       </c>
-      <c r="AF15">
+      <c r="AI15">
         <v>0.02782724318829531</v>
       </c>
-      <c r="AG15">
+      <c r="AJ15">
+        <v>0.001960463976474432</v>
+      </c>
+      <c r="AK15">
         <v>565</v>
       </c>
-      <c r="AH15">
+      <c r="AL15">
         <v>0.01257964384904427</v>
       </c>
-      <c r="AI15">
+      <c r="AM15">
         <v>0.966181996405816</v>
       </c>
-      <c r="AJ15">
-        <v>0.01780754778630943</v>
-      </c>
-      <c r="AK15">
-        <v>0.006698251919620977</v>
-      </c>
-      <c r="AL15">
-        <v>0.009312203888253554</v>
-      </c>
-      <c r="AM15">
-        <v>1</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>60</v>
+      <c r="AN15">
+        <v>0.02009475575886293</v>
+      </c>
+      <c r="AO15">
+        <v>0.004411043947067473</v>
+      </c>
+      <c r="AP15">
+        <v>0.009312203888253554</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
